--- a/13776_Cuenca_Chancay-Lambayeque/_raw_reportes_xlsx/IDConfig_64918_completo.xlsx
+++ b/13776_Cuenca_Chancay-Lambayeque/_raw_reportes_xlsx/IDConfig_64918_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R74c8b05755cd4a57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6b7a3de04e364873"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2868</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2658</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2740</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3353</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3679</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4153</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3123</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3197</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/13776_Cuenca_Chancay-Lambayeque/_raw_reportes_xlsx/IDConfig_64918_completo.xlsx
+++ b/13776_Cuenca_Chancay-Lambayeque/_raw_reportes_xlsx/IDConfig_64918_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6b7a3de04e364873"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re8bde6217cdc4bc3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0724</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6069</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8492</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7855</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4178</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4674</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4008</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4786</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7732</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9651</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3386</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5126</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4606</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5604</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3568</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3565</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4286</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4421</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4317</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4148</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4424</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4473</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4147</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4264</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3132</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2484</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2509</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2795</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2625</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2357</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2406</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2472</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2811</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2827</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -20155,6 +20875,6021 @@
       </x:c>
       <x:c s="3">
         <x:v>      7.4738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6823</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4073</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9205</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0616</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3849</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0628</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1776</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7681</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8243</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8771</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1664</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4309</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4206</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2851</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9683</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8073</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8511</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8499</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4716</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2601</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9118</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0173</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9673</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1851</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1934</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2810</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3186</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4161</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3064</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3516</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7118</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8862</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5101</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6767</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9873</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4217</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4987</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7497</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4319</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2038</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8288</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8325</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8279</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9311</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9617</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0527</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0366</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1174</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4589</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1147</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4904</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2603</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8594</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1377</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5606</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9352</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7614</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7307</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6296</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0139</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2327</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5008</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9330</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1476</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4334</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7142</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0571</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5987</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6955</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9012</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0356</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8299</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.5244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0852</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8472</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9113</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8318</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1709</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1682</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9894</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9809</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0309</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0082</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0414</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0583</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1477</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0414</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1504</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2503</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3716</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4583</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5258</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5124</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4917</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5810</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6337</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7347</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8201</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9035</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0771</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1753</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2062</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2521</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0247</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1010</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8211</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9164</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9421</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4245</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3023</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8025</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6514</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6332</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7160</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8314</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9761</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0977</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8254</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8579</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8465</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8160</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8463</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8882</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9851</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0727</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0728</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0406</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1131</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1786</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5779</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3215</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6912</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2958</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3903</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5629</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6036</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8121</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8883</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9560</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1519</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6439</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6574</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6079</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7987</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3737</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2149</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4961</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1753</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6193</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9363</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2107</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3505</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0082</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9291</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5871</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4469</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6485</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9056</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.3214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8790</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1249</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.3539</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6724</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1353</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4098</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.0964</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.9845</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.1387</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.6990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.7119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.4482</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.9896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4423</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0316</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2869</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2309</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.2264</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.9227</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.5419</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6031</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8659</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3006</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7891</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7639</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.8926</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.4997</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.2570</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7874</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1921</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.2072</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.9080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.4921</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.5711</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9847</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3539</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.4012</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.3427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.2362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.2922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.6829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.7740</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.0597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.4516</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.5110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.2434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4661</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.9959</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.5895</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.3456</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.4869</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.7474</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.9008</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.6291</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.4194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.1644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.6813</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.4041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.3742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.1205</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.2181</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.5816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2429</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1518</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.5622</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6631</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3569</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3590</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3546</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1283</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2618</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3304</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.3753</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.1496</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.8014</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.0226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.6595</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.9967</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.5822</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.9564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.2698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.9301</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.9599</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.4535</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.0320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.2903</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1436</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9859</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4695</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9298</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.7318</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.6848</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.7082</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.4618</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.8431</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.8471</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.9196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.7075</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.2548</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9446</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7934</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2577</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3234</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3435</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4846</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6559</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8883</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1451</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6132</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2770</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4552</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.8637</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.1875</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7372</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9185</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0656</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5249</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0838</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2703</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5218</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6309</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3333</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9028</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3791</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8005</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7819</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2918</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8832</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9640</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7199</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8364</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1831</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3537</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6160</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.0948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1042</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.7844</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.1541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.3385</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4985</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5804</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4294</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4695</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9126</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.4416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.8168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2364</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3043</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4843</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9136</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9519</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2559</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3747</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2283</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/11/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2360</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/11/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3792</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/11/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/11/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9616</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/11/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1941</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
